--- a/Docs/QA-Testing/Test_Case_BVA.xlsx
+++ b/Docs/QA-Testing/Test_Case_BVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6E83CA-361E-E749-83DF-411B99E4A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2EB4DE-9D32-473F-B877-A5D15E2D5858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Doc_Cong_Thuc" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>Ví dụ:</t>
   </si>
   <si>
-    <t>password: 3–20 ký tự | productStock: ≥ 0 | quantity: ≥ 1 | productPrice: &gt; 0 (hiện code chưa enforce)</t>
-  </si>
-  <si>
     <t>5. QUY TRÌNH LÀM VIỆC</t>
   </si>
   <si>
@@ -980,6 +977,9 @@
   </si>
   <si>
     <t>THÀNH</t>
+  </si>
+  <si>
+    <t>password: 3–20 ký tự | productStock: ≥ 0 | quantity: ≥ 1 | productPrice: &gt; 0 (đã enforce @Positive/@DecimalMin sau fix Sprint)</t>
   </si>
 </sst>
 </file>
@@ -1348,6 +1348,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1378,10 +1382,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1685,7 +1685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -1695,29 +1695,29 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1741,18 +1741,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="47" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-    </row>
-    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
         <v>14</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>17</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>19</v>
       </c>
@@ -1820,12 +1820,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="43" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1841,12 +1841,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1854,42 +1854,42 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
       <c r="B20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="43" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="44" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="44" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="44" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="44" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="44" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="44" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="44" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="44" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="44" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="44" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1905,7 +1905,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1913,206 +1913,206 @@
     <col min="4" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="4" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="43" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="43" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2145,1176 +2145,1176 @@
     <col min="15" max="15" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+    </row>
+    <row r="5" spans="1:15" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-    </row>
-    <row r="5" spans="1:15" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="I6" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J6" s="6">
         <v>200</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="20"/>
       <c r="N6" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>108</v>
-      </c>
       <c r="E7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I7" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J7" s="14">
         <v>200</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M7" s="19"/>
       <c r="N7" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="E8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="6">
         <v>200</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="18" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="18" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="E9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I9" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J9" s="14">
         <v>200</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="18" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="18" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="E10" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I10" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="6">
         <v>200</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="F11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I11" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="14">
         <v>200</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M11" s="19"/>
       <c r="N11" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>118</v>
-      </c>
       <c r="F12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="6">
         <v>200</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="F13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I13" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="14">
         <v>200</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M13" s="19"/>
       <c r="N13" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>122</v>
-      </c>
       <c r="F14" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J14" s="6">
         <v>200</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="G15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I15" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="14">
         <v>200</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M15" s="19"/>
       <c r="N15" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="G16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I16" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J16" s="6">
         <v>200</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="G17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="I17" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="14">
         <v>200</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M17" s="19"/>
       <c r="N17" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>130</v>
-      </c>
       <c r="G18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="I18" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="6">
         <v>200</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="H19" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J19" s="14">
         <v>200</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="H20" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J20" s="6">
         <v>200</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>136</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" s="14">
         <v>200</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>138</v>
-      </c>
       <c r="H22" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="6">
         <v>200</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>140</v>
-      </c>
       <c r="I23" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="14">
         <v>200</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>142</v>
-      </c>
       <c r="I24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="6">
         <v>200</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="18" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="18" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>144</v>
-      </c>
       <c r="I25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J25" s="14">
         <v>200</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="18" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="18" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="I26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J26" s="6">
         <v>200</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="11" t="s">
+      <c r="G27" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="J27" s="14">
         <v>200</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="L27" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M27" s="19" t="s">
+      <c r="N27" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" s="19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="18" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="N27" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="18" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+      <c r="B28" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F28" s="12" t="s">
+      <c r="G28" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="G28" s="17" t="s">
-        <v>156</v>
-      </c>
       <c r="H28" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J28" s="6">
         <v>200</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L28" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="M28" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="N28" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="N28" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="B29" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>161</v>
-      </c>
       <c r="H29" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J29" s="14">
         <v>200</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M29" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O29" s="19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="18" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="N29" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="18" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+      <c r="B30" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>165</v>
-      </c>
       <c r="H30" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J30" s="6">
         <v>200</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L30" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="M30" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="M30" s="20" t="s">
+      <c r="N30" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O30" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="N30" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="O30" s="20" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="43" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3330,7 +3330,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3338,71 +3338,71 @@
     <col min="4" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="29.6640625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+      <c r="B7" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="C7" s="25" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="25">
         <v>3</v>
@@ -3420,15 +3420,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C8" s="26" t="s">
         <v>179</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>180</v>
       </c>
       <c r="D8" s="26">
         <v>3</v>
@@ -3446,21 +3446,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="C9" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="D9" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="E9" s="25" t="s">
         <v>184</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>185</v>
       </c>
       <c r="F9" s="25">
         <v>40</v>
@@ -3472,15 +3472,15 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="C10" s="26" t="s">
         <v>187</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>188</v>
       </c>
       <c r="D10" s="26">
         <v>0</v>
@@ -3498,15 +3498,15 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="C11" s="25" t="s">
         <v>190</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>191</v>
       </c>
       <c r="D11" s="25">
         <v>0</v>
@@ -3524,30 +3524,30 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="56" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
-        <v>193</v>
-      </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="21"/>
     </row>
   </sheetData>
@@ -3564,9 +3564,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
@@ -3576,105 +3576,105 @@
     <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56" t="s">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
       <c r="E4" s="45"/>
       <c r="F4" s="45"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
       <c r="E5" s="45"/>
       <c r="F5" s="45"/>
     </row>
-    <row r="7" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="C7" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="D7" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="J7" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="J7" s="34" t="s">
+      <c r="K7" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="K7" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="L7" s="34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="B8" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="C8" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="32" t="s">
+      <c r="E8" s="32" t="s">
         <v>203</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>204</v>
       </c>
       <c r="F8" s="32">
         <v>40</v>
@@ -3683,34 +3683,34 @@
         <v>100</v>
       </c>
       <c r="H8" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="32"/>
+    </row>
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="I8" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="K8" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="32"/>
-    </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
-        <v>206</v>
-      </c>
       <c r="B9" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F9" s="35">
         <v>40</v>
@@ -3719,34 +3719,34 @@
         <v>100</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L9" s="35"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>208</v>
-      </c>
       <c r="E10" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F10" s="32">
         <v>40</v>
@@ -3755,34 +3755,34 @@
         <v>100</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L10" s="32"/>
     </row>
-    <row r="11" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>210</v>
-      </c>
       <c r="E11" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F11" s="35">
         <v>40</v>
@@ -3791,34 +3791,34 @@
         <v>100</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L11" s="35"/>
     </row>
-    <row r="12" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>212</v>
-      </c>
       <c r="E12" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F12" s="32">
         <v>40</v>
@@ -3827,34 +3827,34 @@
         <v>100</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I12" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L12" s="32"/>
     </row>
-    <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>214</v>
-      </c>
       <c r="E13" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F13" s="35">
         <v>40</v>
@@ -3863,34 +3863,34 @@
         <v>100</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K13" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>216</v>
-      </c>
       <c r="E14" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F14" s="32">
         <v>40</v>
@@ -3899,34 +3899,34 @@
         <v>100</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I14" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L14" s="32"/>
     </row>
-    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="35" t="s">
+      <c r="E15" s="35" t="s">
         <v>218</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>219</v>
       </c>
       <c r="F15" s="35">
         <v>40</v>
@@ -3935,34 +3935,34 @@
         <v>100</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I15" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L15" s="35"/>
     </row>
-    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="32" t="s">
+      <c r="E16" s="32" t="s">
         <v>221</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>222</v>
       </c>
       <c r="F16" s="32">
         <v>40</v>
@@ -3971,106 +3971,106 @@
         <v>100</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L16" s="32"/>
     </row>
-    <row r="17" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="B17" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>224</v>
-      </c>
       <c r="E17" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="35">
         <v>100</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I17" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K17" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" s="35"/>
     </row>
-    <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>226</v>
-      </c>
       <c r="E18" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18" s="32">
         <v>100</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I18" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" s="32"/>
     </row>
-    <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="B19" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>228</v>
-      </c>
       <c r="E19" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F19" s="35">
         <v>999999</v>
@@ -4079,34 +4079,34 @@
         <v>100</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I19" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L19" s="35"/>
     </row>
-    <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>230</v>
-      </c>
       <c r="E20" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F20" s="32">
         <v>1000000</v>
@@ -4115,34 +4115,34 @@
         <v>100</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I20" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L20" s="32"/>
     </row>
-    <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="B21" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>232</v>
-      </c>
       <c r="E21" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F21" s="35">
         <v>40</v>
@@ -4151,34 +4151,34 @@
         <v>0</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I21" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K21" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L21" s="35"/>
     </row>
-    <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="B22" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>234</v>
-      </c>
       <c r="E22" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F22" s="32">
         <v>40</v>
@@ -4187,34 +4187,34 @@
         <v>1</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I22" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L22" s="32"/>
     </row>
-    <row r="23" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>236</v>
-      </c>
       <c r="E23" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F23" s="35">
         <v>40</v>
@@ -4223,34 +4223,34 @@
         <v>9998</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I23" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L23" s="35"/>
     </row>
-    <row r="24" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="B24" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>238</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F24" s="32">
         <v>40</v>
@@ -4259,34 +4259,34 @@
         <v>9999</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L24" s="32"/>
     </row>
-    <row r="25" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="B25" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>240</v>
-      </c>
       <c r="E25" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F25" s="35">
         <v>40</v>
@@ -4295,34 +4295,34 @@
         <v>100</v>
       </c>
       <c r="H25" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="I25" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="L25" s="35"/>
+    </row>
+    <row r="26" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="I25" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="J25" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="K25" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="L25" s="35"/>
-    </row>
-    <row r="26" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="B26" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="B26" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>243</v>
-      </c>
       <c r="E26" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F26" s="32">
         <v>40</v>
@@ -4331,34 +4331,34 @@
         <v>100</v>
       </c>
       <c r="H26" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K26" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" s="32"/>
+    </row>
+    <row r="27" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="I26" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="J26" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="K26" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="L26" s="32"/>
-    </row>
-    <row r="27" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
+      <c r="B27" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B27" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="35" t="s">
-        <v>246</v>
-      </c>
       <c r="E27" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F27" s="35">
         <v>40</v>
@@ -4367,34 +4367,34 @@
         <v>100</v>
       </c>
       <c r="H27" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="I27" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" s="35"/>
+    </row>
+    <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="I27" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="J27" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="K27" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="L27" s="35"/>
-    </row>
-    <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32" t="s">
+      <c r="B28" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="B28" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>249</v>
-      </c>
       <c r="E28" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F28" s="32">
         <v>40</v>
@@ -4403,198 +4403,198 @@
         <v>100</v>
       </c>
       <c r="H28" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="L28" s="32"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="I28" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="J28" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="K28" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="L28" s="32"/>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="34" t="s">
+      <c r="C29" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>252</v>
-      </c>
       <c r="E29" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="F29" s="34" t="s">
-        <v>200</v>
-      </c>
       <c r="G29" s="34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J29" s="34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
     </row>
-    <row r="30" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="32" t="s">
         <v>253</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>254</v>
       </c>
       <c r="E30" s="32">
         <v>400</v>
       </c>
       <c r="F30" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="G30" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>256</v>
-      </c>
       <c r="I30" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J30" s="32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K30" s="31"/>
       <c r="L30" s="31"/>
     </row>
-    <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="35" t="s">
         <v>257</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>258</v>
       </c>
       <c r="E31" s="35">
         <v>400</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I31" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J31" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K31" s="31"/>
       <c r="L31" s="31"/>
     </row>
-    <row r="32" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E32" s="32">
         <v>400</v>
       </c>
       <c r="F32" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="G32" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="H32" s="32" t="s">
-        <v>262</v>
-      </c>
       <c r="I32" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J32" s="32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K32" s="31"/>
       <c r="L32" s="31"/>
     </row>
-    <row r="33" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="35" t="s">
         <v>263</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>264</v>
       </c>
       <c r="E33" s="35">
         <v>400</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
     </row>
-    <row r="34" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D34" s="32">
         <v>0</v>
@@ -4603,32 +4603,32 @@
         <v>400</v>
       </c>
       <c r="F34" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="G34" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="H34" s="32" t="s">
-        <v>268</v>
-      </c>
       <c r="I34" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J34" s="32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K34" s="31"/>
       <c r="L34" s="31"/>
     </row>
-    <row r="35" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D35" s="35">
         <v>-1</v>
@@ -4637,32 +4637,32 @@
         <v>400</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K35" s="31"/>
       <c r="L35" s="31"/>
     </row>
-    <row r="36" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D36" s="32">
         <v>-1</v>
@@ -4671,53 +4671,53 @@
         <v>400</v>
       </c>
       <c r="F36" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G36" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>273</v>
-      </c>
       <c r="I36" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K36" s="31"/>
       <c r="L36" s="31"/>
     </row>
-    <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="35" t="s">
         <v>274</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>275</v>
       </c>
       <c r="E37" s="35">
         <v>400</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J37" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K37" s="31"/>
       <c r="L37" s="31"/>
@@ -4736,76 +4736,76 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="28.33203125" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="33.1640625" customWidth="1"/>
+    <col min="9" max="9" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="C6" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="G6" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="H6" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="23">
         <v>3</v>
@@ -4823,15 +4823,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -4849,19 +4849,19 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="55" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="21"/>
       <c r="B13" s="45"/>
       <c r="C13" s="21"/>
@@ -4869,7 +4869,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
       <c r="B14" s="45"/>
       <c r="C14" s="21"/>
@@ -4877,7 +4877,7 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="21"/>
       <c r="B15" s="45"/>
       <c r="C15" s="21"/>
@@ -4885,7 +4885,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="21"/>
       <c r="B16" s="45"/>
       <c r="C16" s="21"/>
@@ -4906,9 +4906,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" style="42" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" style="42" customWidth="1"/>
     <col min="2" max="2" width="20" style="42" customWidth="1"/>
     <col min="3" max="5" width="12" style="42" customWidth="1"/>
     <col min="6" max="6" width="36" style="42" customWidth="1"/>
@@ -4916,381 +4916,381 @@
     <col min="8" max="8" width="10" style="42" customWidth="1"/>
     <col min="9" max="9" width="28" style="42" customWidth="1"/>
     <col min="10" max="10" width="18" style="42" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" style="42" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="42"/>
+    <col min="11" max="12" width="8.77734375" style="42" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="B3" s="59"/>
+      <c r="B3" s="61"/>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="C7" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="D7" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="34" t="s">
-        <v>200</v>
-      </c>
       <c r="H7" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>286</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>287</v>
       </c>
       <c r="E8" s="37">
         <v>5</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I8" s="37"/>
       <c r="J8" s="37"/>
     </row>
-    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9" s="39">
         <v>5</v>
       </c>
       <c r="F9" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="G9" s="39" t="s">
-        <v>290</v>
-      </c>
       <c r="H9" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I9" s="39"/>
       <c r="J9" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
-        <v>292</v>
-      </c>
       <c r="B10" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E10" s="37">
         <v>5</v>
       </c>
       <c r="F10" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="G10" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>290</v>
-      </c>
       <c r="H10" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="40" t="s">
         <v>293</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>294</v>
       </c>
       <c r="E11" s="39">
         <v>5</v>
       </c>
       <c r="F11" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="G11" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="G11" s="39" t="s">
-        <v>290</v>
-      </c>
       <c r="H11" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I11" s="39"/>
       <c r="J11" s="39"/>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="38" t="s">
         <v>295</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>296</v>
       </c>
       <c r="E12" s="37">
         <v>5</v>
       </c>
       <c r="F12" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="G12" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="G12" s="37" t="s">
-        <v>290</v>
-      </c>
       <c r="H12" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E13" s="39">
         <v>1</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I13" s="39"/>
       <c r="J13" s="39"/>
     </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B14" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37"/>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B15" s="39" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E15" s="39">
         <v>998</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I15" s="39"/>
       <c r="J15" s="39"/>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B16" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E16" s="37">
         <v>999</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>252</v>
-      </c>
       <c r="E17" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="F17" s="36" t="s">
-        <v>200</v>
-      </c>
       <c r="G17" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="J17" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="J17" s="36" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B18" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18" s="37">
         <v>0</v>
@@ -5299,30 +5299,30 @@
         <v>400</v>
       </c>
       <c r="F18" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="G18" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="37" t="s">
+      <c r="I18" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
         <v>303</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
-        <v>304</v>
       </c>
       <c r="B19" s="39" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D19" s="39">
         <v>-1</v>
@@ -5331,83 +5331,83 @@
         <v>400</v>
       </c>
       <c r="F19" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="G19" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="37" t="s">
-        <v>306</v>
-      </c>
       <c r="B20" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E20" s="37">
         <v>400</v>
       </c>
       <c r="F20" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="G20" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="I20" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="39" t="s">
-        <v>308</v>
-      </c>
       <c r="B21" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E21" s="39">
         <v>400</v>
       </c>
       <c r="F21" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="G21" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>310</v>
-      </c>
       <c r="I21" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="J21" s="62" t="s">
-        <v>315</v>
+        <v>105</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
